--- a/KURIKULUM2026_REVISI/007_FORMULASI_CPMK_DAN_SUB_CPMK_PORTFOLIO_LENGKAP.xlsx
+++ b/KURIKULUM2026_REVISI/007_FORMULASI_CPMK_DAN_SUB_CPMK_PORTFOLIO_LENGKAP.xlsx
@@ -26511,7 +26511,7 @@
       </c>
       <c r="B1330" s="7" t="inlineStr">
         <is>
-          <t>**STI-624 — Integrasi Layanan Cerdas Berbasis AI** (*AI-Based Smart Services Integration*)</t>
+          <t>**STI-726 — Integrasi Layanan Cerdas Berbasis AI** (*AI-Based Smart Services Integration*)</t>
         </is>
       </c>
     </row>
@@ -27215,7 +27215,7 @@
       </c>
       <c r="B1366" s="7" t="inlineStr">
         <is>
-          <t>**STI-625 — Smart City &amp; Pemerintahan Digital** (*Smart City &amp; Digital Governance*)</t>
+          <t>**STI-727 — Smart City &amp; Pemerintahan Digital** (*Smart City &amp; Digital Governance*)</t>
         </is>
       </c>
     </row>
@@ -27919,7 +27919,7 @@
       </c>
       <c r="B1402" s="7" t="inlineStr">
         <is>
-          <t>**STI-626 — Deep Learning &amp; Neural Networks** (*Deep Learning &amp; Neural Networks*)</t>
+          <t>**STI-624 — Deep Learning &amp; Neural Networks** (*Deep Learning &amp; Neural Networks*)</t>
         </is>
       </c>
     </row>
@@ -28623,7 +28623,7 @@
       </c>
       <c r="B1438" s="7" t="inlineStr">
         <is>
-          <t>**STI-627 — Digital Platform Engineering** (*Digital Platform Engineering*)</t>
+          <t>**STI-625 — Digital Platform Engineering** (*Digital Platform Engineering*)</t>
         </is>
       </c>
     </row>
@@ -35611,7 +35611,7 @@
       </c>
       <c r="B1797" s="9" t="inlineStr">
         <is>
-          <t>`STI-413` Machine Learning &amp; `STI-624` Integrasi AI</t>
+          <t>`STI-413` Machine Learning &amp; `STI-726` Integrasi AI</t>
         </is>
       </c>
     </row>
@@ -36997,7 +36997,7 @@
       </c>
       <c r="B1868" s="9" t="inlineStr">
         <is>
-          <t>`STI-626` Deep Learning &amp; `STI-521` IoT</t>
+          <t>`STI-624` Deep Learning &amp; `STI-521` IoT</t>
         </is>
       </c>
     </row>
